--- a/01-INTRO/M02/bus311-intro-m02-l01-market-cap-activity.xlsx
+++ b/01-INTRO/M02/bus311-intro-m02-l01-market-cap-activity.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29712"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/BUS311 Corporate Finance/BME - FA25- Teaching Materials - Brealey/Chapter 2 - Financial Institutions and Markets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="23" documentId="8_{6B3257E2-1813-4564-8427-ADC7C7CAA416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B03D8B4-59AF-4A29-B9A8-1F7BAF5EBD22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABD960A4-8EF3-4BD1-B1A9-39CB98FE2B11}"/>
